--- a/course-design-2/outputs/tables/ch7/51_stage26_4_formal_feature_audit.xlsx
+++ b/course-design-2/outputs/tables/ch7/51_stage26_4_formal_feature_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_正式模型输入字段审计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_移除字段清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_特征组维度对照" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="01_正式模型输入字段审计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_移除字段清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_特征组维度对照" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -746,7 +746,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>数据来源质量：表头口径与平台分类的一致性检查标记，属数据质量元数据，不进入正式薪资预测模型</t>
+          <t>数据来源质量：表头统计范围与平台分类的一致性检查标记，属数据质量元数据，不进入正式薪资预测模型</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>岗位标注的工作城市（原始口径）</t>
+          <t>岗位标注的工作城市（原始统计范围）</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>技能抽取所用匹配口径的标记</t>
+          <t>技能抽取所用匹配统计范围的标记</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>技能匹配状态：技能抽取时的匹配口径标记，属技能匹配状态元数据，不进入正式薪资预测模型</t>
+          <t>技能匹配状态：技能抽取时的匹配统计范围标记，属技能匹配状态元数据，不进入正式薪资预测模型</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>表头口径与平台分类的一致性检查标记，属数据质量元数据</t>
+          <t>表头统计范围与平台分类的一致性检查标记，属数据质量元数据</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>技能抽取时的匹配口径标记，属技能匹配状态元数据</t>
+          <t>技能抽取时的匹配统计范围标记，属技能匹配状态元数据</t>
         </is>
       </c>
     </row>

--- a/course-design-2/outputs/tables/ch7/51_stage26_4_formal_feature_audit.xlsx
+++ b/course-design-2/outputs/tables/ch7/51_stage26_4_formal_feature_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_正式模型输入字段审计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_移除字段清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_特征组维度对照" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_正式模型输入字段审计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_移除字段清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_特征组维度对照" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -746,7 +746,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>数据来源质量：表头统计范围与平台分类的一致性检查标记，属数据质量元数据，不进入正式薪资预测模型</t>
+          <t>数据来源质量：表头口径与平台分类的一致性检查标记，属数据质量元数据，不进入正式薪资预测模型</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>岗位标注的工作城市（原始统计范围）</t>
+          <t>岗位标注的工作城市（原始口径）</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>技能抽取所用匹配统计范围的标记</t>
+          <t>技能抽取所用匹配口径的标记</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>技能匹配状态：技能抽取时的匹配统计范围标记，属技能匹配状态元数据，不进入正式薪资预测模型</t>
+          <t>技能匹配状态：技能抽取时的匹配口径标记，属技能匹配状态元数据，不进入正式薪资预测模型</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>表头统计范围与平台分类的一致性检查标记，属数据质量元数据</t>
+          <t>表头口径与平台分类的一致性检查标记，属数据质量元数据</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>技能抽取时的匹配统计范围标记，属技能匹配状态元数据</t>
+          <t>技能抽取时的匹配口径标记，属技能匹配状态元数据</t>
         </is>
       </c>
     </row>
